--- a/data/trans_dic/P19-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P19-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que en los últimos 6 meses han ido al dentista</t>
+          <t>Población que en los últimos 6 meses han ido al dentista (tasa de respuesta: 99,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,27; 24,61</t>
+          <t>15,43; 24,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20,61; 30,87</t>
+          <t>20,52; 31,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24,21; 35,78</t>
+          <t>24,99; 36,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30,65; 43,97</t>
+          <t>30,02; 44,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,16; 28,45</t>
+          <t>17,79; 28,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,57; 32,6</t>
+          <t>21,24; 33,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,43; 41,02</t>
+          <t>28,76; 39,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>34,87; 44,45</t>
+          <t>34,8; 44,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>17,91; 25,03</t>
+          <t>18,06; 25,05</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22,61; 30,41</t>
+          <t>22,72; 30,48</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28,58; 36,81</t>
+          <t>28,65; 36,77</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>34,04; 42,85</t>
+          <t>34,35; 42,78</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24,79; 33,22</t>
+          <t>24,88; 33,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,07; 28,69</t>
+          <t>21,02; 28,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24,71; 32,54</t>
+          <t>24,24; 32,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19,96; 29,76</t>
+          <t>20,16; 29,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,6; 39,05</t>
+          <t>30,95; 39,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,55; 29,41</t>
+          <t>21,78; 29,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,46; 36,6</t>
+          <t>27,66; 36,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>23,74; 30,78</t>
+          <t>23,71; 30,84</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>28,71; 34,93</t>
+          <t>29,02; 34,9</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22,57; 28,08</t>
+          <t>22,34; 27,86</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27,86; 33,35</t>
+          <t>27,32; 33,39</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22,85; 29,06</t>
+          <t>22,79; 28,92</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17,75; 27,35</t>
+          <t>18,19; 27,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,83; 28,29</t>
+          <t>18,49; 28,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25,2; 34,99</t>
+          <t>25,03; 34,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,52; 25,34</t>
+          <t>16,27; 25,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23,74; 33,19</t>
+          <t>23,95; 33,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31,0; 41,8</t>
+          <t>30,68; 41,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,16; 36,76</t>
+          <t>26,04; 36,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>26,43; 34,89</t>
+          <t>26,24; 34,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22,22; 28,86</t>
+          <t>22,43; 29,14</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25,75; 33,67</t>
+          <t>26,47; 33,4</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>26,97; 34,28</t>
+          <t>27,23; 34,15</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>22,9; 29,01</t>
+          <t>22,73; 28,95</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,94; 31,25</t>
+          <t>21,88; 30,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>22,36; 31,64</t>
+          <t>22,42; 31,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25,76; 35,68</t>
+          <t>25,75; 36,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32,19; 46,15</t>
+          <t>31,46; 45,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>28,46; 37,9</t>
+          <t>28,16; 37,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,71; 30,52</t>
+          <t>21,31; 30,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,87; 43,27</t>
+          <t>32,67; 43,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>25,03; 53,11</t>
+          <t>25,86; 52,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>26,56; 32,93</t>
+          <t>26,54; 33,25</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23,1; 29,85</t>
+          <t>23,45; 30,34</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30,92; 38,17</t>
+          <t>31,03; 38,06</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30,91; 47,47</t>
+          <t>30,56; 47,9</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>27,23; 40,12</t>
+          <t>26,99; 39,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13,6; 24,93</t>
+          <t>14,51; 25,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,92; 22,07</t>
+          <t>11,82; 22,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,74; 17,36</t>
+          <t>8,26; 16,55</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,09; 35,89</t>
+          <t>22,69; 35,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,41; 39,51</t>
+          <t>26,54; 38,83</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,06; 32,1</t>
+          <t>20,31; 31,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,89; 22,2</t>
+          <t>14,63; 22,36</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>26,59; 35,93</t>
+          <t>26,36; 35,6</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22,38; 30,79</t>
+          <t>21,99; 30,79</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17,57; 25,3</t>
+          <t>17,46; 25,4</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,88; 18,2</t>
+          <t>12,67; 18,22</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15,17; 24,77</t>
+          <t>15,6; 24,56</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>25,17; 36,62</t>
+          <t>25,08; 36,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29,62; 41,64</t>
+          <t>29,97; 41,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19,71; 29,67</t>
+          <t>19,23; 29,02</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>28,77; 40,16</t>
+          <t>28,25; 39,67</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,87; 36,22</t>
+          <t>24,7; 36,01</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35,97; 46,99</t>
+          <t>35,27; 48,11</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>24,18; 32,84</t>
+          <t>24,18; 33,21</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>23,57; 30,96</t>
+          <t>23,54; 31,22</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>26,3; 34,52</t>
+          <t>26,33; 34,44</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>34,3; 42,73</t>
+          <t>33,97; 42,57</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>23,37; 29,79</t>
+          <t>23,04; 29,98</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>25,22; 32,73</t>
+          <t>25,18; 32,61</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>21,06; 28,02</t>
+          <t>21,15; 28,17</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24,47; 31,71</t>
+          <t>24,53; 32,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30,17; 39,0</t>
+          <t>30,45; 39,43</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>34,02; 41,93</t>
+          <t>34,24; 41,71</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,11; 37,29</t>
+          <t>29,82; 37,18</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,1; 40,76</t>
+          <t>33,73; 40,96</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>15,49; 40,58</t>
+          <t>15,68; 40,76</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>30,64; 36,12</t>
+          <t>31,05; 36,5</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26,49; 31,83</t>
+          <t>26,79; 31,8</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30,12; 35,33</t>
+          <t>30,22; 35,52</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>20,53; 38,27</t>
+          <t>18,6; 37,94</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>17,93; 23,8</t>
+          <t>17,76; 23,58</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>20,53; 26,63</t>
+          <t>20,49; 26,64</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26,52; 33,15</t>
+          <t>26,44; 33,27</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,33; 21,3</t>
+          <t>6,75; 20,54</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>23,59; 30,0</t>
+          <t>23,45; 30,07</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,56; 34,3</t>
+          <t>27,51; 34,15</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,38; 37,33</t>
+          <t>30,07; 36,75</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>21,76; 27,11</t>
+          <t>21,25; 26,78</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>21,55; 26,06</t>
+          <t>21,63; 26,11</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>25,23; 29,99</t>
+          <t>25,17; 29,59</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29,3; 34,21</t>
+          <t>29,66; 34,49</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>11,15; 22,74</t>
+          <t>11,7; 22,82</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>23,24; 26,34</t>
+          <t>23,38; 26,54</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>23,17; 26,08</t>
+          <t>23,24; 26,21</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>27,33; 30,59</t>
+          <t>27,52; 30,51</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18,92; 27,71</t>
+          <t>19,49; 27,58</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>29,8; 32,86</t>
+          <t>29,78; 33,02</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>28,85; 32,02</t>
+          <t>28,62; 31,75</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>32,89; 36,09</t>
+          <t>32,96; 36,15</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>24,2; 32,76</t>
+          <t>24,36; 32,7</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>27,03; 29,2</t>
+          <t>26,97; 29,31</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>26,49; 28,68</t>
+          <t>26,42; 28,62</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>30,55; 32,94</t>
+          <t>30,72; 33,0</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>24,28; 29,69</t>
+          <t>23,69; 29,62</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que en los últimos 6 meses han ido al dentista</t>
+          <t>Población que en los últimos 6 meses han ido al dentista (tasa de respuesta: 99,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>41700; 67179</t>
+          <t>42128; 68026</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>60517; 90619</t>
+          <t>60254; 91727</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>71125; 105120</t>
+          <t>73403; 107065</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>95459; 136934</t>
+          <t>93488; 137152</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>47381; 74197</t>
+          <t>46390; 74379</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>61957; 93654</t>
+          <t>61012; 94855</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>84958; 118420</t>
+          <t>83022; 115344</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>100552; 128179</t>
+          <t>100347; 129082</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>95614; 133640</t>
+          <t>96427; 133726</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>131298; 176638</t>
+          <t>131992; 177016</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>166466; 214377</t>
+          <t>166897; 214189</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>204195; 256994</t>
+          <t>206042; 256593</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>122237; 163815</t>
+          <t>122699; 164042</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>106532; 145058</t>
+          <t>106246; 145069</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>124163; 163540</t>
+          <t>121842; 163059</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>103317; 154023</t>
+          <t>104312; 154991</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>153940; 196426</t>
+          <t>155699; 196735</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>112865; 154036</t>
+          <t>114063; 152635</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>148855; 191442</t>
+          <t>144663; 188742</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>121558; 157623</t>
+          <t>121380; 157924</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>286017; 347889</t>
+          <t>289095; 347620</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>232288; 289033</t>
+          <t>229959; 286794</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>285720; 342050</t>
+          <t>280215; 342497</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>235265; 299173</t>
+          <t>234607; 297693</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>56588; 87209</t>
+          <t>57992; 87935</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>60763; 91271</t>
+          <t>59672; 91585</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>80288; 111461</t>
+          <t>79729; 111041</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>51811; 79467</t>
+          <t>51039; 78790</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>79638; 111318</t>
+          <t>80335; 113611</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>105716; 142547</t>
+          <t>104617; 141232</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>87975; 123644</t>
+          <t>87562; 122927</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>91954; 121381</t>
+          <t>91283; 121360</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>145385; 188848</t>
+          <t>146732; 190636</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>170879; 223461</t>
+          <t>175683; 221668</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>176599; 224516</t>
+          <t>178337; 223663</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>151469; 191941</t>
+          <t>150384; 191507</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>78689; 112097</t>
+          <t>78493; 110905</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>83612; 118328</t>
+          <t>83833; 119560</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>95317; 132017</t>
+          <t>95262; 133700</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>100444; 143973</t>
+          <t>98144; 143198</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>105715; 140794</t>
+          <t>104610; 140605</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>84444; 118720</t>
+          <t>82889; 117649</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>127301; 167569</t>
+          <t>126520; 167936</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>118062; 250514</t>
+          <t>121977; 249244</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>193917; 240399</t>
+          <t>193775; 242736</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>176226; 227743</t>
+          <t>178917; 231456</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>234166; 289005</t>
+          <t>235007; 288190</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>242219; 372033</t>
+          <t>239477; 375408</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>55354; 81573</t>
+          <t>54863; 81074</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>28909; 52998</t>
+          <t>30848; 54078</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>25172; 46622</t>
+          <t>24964; 47328</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15627; 31027</t>
+          <t>14771; 29590</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>47956; 74529</t>
+          <t>47124; 74052</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>57736; 86390</t>
+          <t>58018; 84888</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>43857; 70159</t>
+          <t>44387; 68931</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>30700; 45762</t>
+          <t>30146; 46087</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>109266; 147650</t>
+          <t>108346; 146320</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>96515; 132770</t>
+          <t>94849; 132779</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>75503; 108724</t>
+          <t>75039; 109165</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>49581; 70059</t>
+          <t>48767; 70103</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>41072; 67068</t>
+          <t>42239; 66498</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>68974; 100343</t>
+          <t>68704; 101199</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>77927; 109566</t>
+          <t>78853; 109007</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>53133; 80011</t>
+          <t>51860; 78242</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>80009; 111702</t>
+          <t>78571; 110342</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>69650; 101432</t>
+          <t>69178; 100838</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>98241; 128339</t>
+          <t>96320; 131387</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>62146; 84429</t>
+          <t>62162; 85358</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>129396; 169966</t>
+          <t>129219; 171409</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>145726; 191260</t>
+          <t>145845; 190797</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>183913; 229109</t>
+          <t>182149; 228300</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>123099; 156923</t>
+          <t>121336; 157903</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>154882; 201009</t>
+          <t>154661; 200287</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>139556; 185744</t>
+          <t>140173; 186703</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>160679; 208172</t>
+          <t>161052; 210234</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>184469; 238472</t>
+          <t>186229; 241136</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>217140; 267597</t>
+          <t>218517; 266193</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>208938; 258767</t>
+          <t>206896; 258005</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>228820; 281760</t>
+          <t>233167; 283174</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>129569; 339392</t>
+          <t>131167; 340845</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>383773; 452371</t>
+          <t>388838; 457140</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>359398; 431786</t>
+          <t>363396; 431421</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>406032; 476224</t>
+          <t>407344; 478724</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>297174; 554029</t>
+          <t>269318; 549224</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>133360; 177030</t>
+          <t>132132; 175374</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>159969; 207479</t>
+          <t>159623; 207568</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>206452; 258137</t>
+          <t>205825; 259022</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>58400; 196451</t>
+          <t>62270; 189371</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>184802; 235083</t>
+          <t>183748; 235629</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>227068; 282570</t>
+          <t>226641; 281384</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>250957; 308444</t>
+          <t>248468; 303602</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>154587; 192558</t>
+          <t>150952; 190214</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>329181; 398078</t>
+          <t>330332; 398765</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>404392; 480719</t>
+          <t>403531; 474275</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>470179; 548942</t>
+          <t>475900; 553472</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>182092; 371254</t>
+          <t>190939; 372530</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>761136; 862782</t>
+          <t>765770; 869320</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>793371; 893185</t>
+          <t>795892; 897514</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>927665; 1038411</t>
+          <t>934257; 1035721</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>650025; 952093</t>
+          <t>669893; 947806</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1006886; 1110122</t>
+          <t>1006060; 1115428</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1026159; 1139075</t>
+          <t>1018088; 1129440</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1165881; 1279347</t>
+          <t>1168344; 1281496</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>878391; 1189142</t>
+          <t>884215; 1187018</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1798612; 1942870</t>
+          <t>1794572; 1949930</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1849388; 2002245</t>
+          <t>1844792; 1998460</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2120052; 2285927</t>
+          <t>2131619; 2290065</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1715635; 2097718</t>
+          <t>1673995; 2093062</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P19-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>36,28%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,43; 24,92</t>
+          <t>15,45; 24,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20,52; 31,24</t>
+          <t>21,09; 31,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24,99; 36,45</t>
+          <t>25,1; 36,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30,02; 44,04</t>
+          <t>29,67; 40,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,79; 28,52</t>
+          <t>17,32; 27,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,24; 33,02</t>
+          <t>21,36; 32,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,76; 39,95</t>
+          <t>29,58; 40,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>34,8; 44,77</t>
+          <t>32,84; 42,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,06; 25,05</t>
+          <t>17,54; 24,93</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22,72; 30,48</t>
+          <t>22,79; 30,28</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28,65; 36,77</t>
+          <t>28,44; 36,59</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>34,35; 42,78</t>
+          <t>33,05; 39,72</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,27%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24,88; 33,27</t>
+          <t>24,34; 33,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>21,02; 28,7</t>
+          <t>20,64; 28,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24,24; 32,44</t>
+          <t>24,08; 32,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20,16; 29,95</t>
+          <t>19,16; 28,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,95; 39,11</t>
+          <t>31,02; 39,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,78; 29,14</t>
+          <t>21,66; 29,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,66; 36,08</t>
+          <t>28,22; 36,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>23,71; 30,84</t>
+          <t>23,39; 30,4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29,02; 34,9</t>
+          <t>29,02; 35,22</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22,34; 27,86</t>
+          <t>22,48; 28,07</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27,32; 33,39</t>
+          <t>27,8; 33,44</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22,79; 28,92</t>
+          <t>22,33; 28,32</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,96%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,19; 27,58</t>
+          <t>17,87; 27,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,49; 28,38</t>
+          <t>18,64; 28,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25,03; 34,86</t>
+          <t>25,14; 34,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,27; 25,12</t>
+          <t>16,4; 24,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23,95; 33,87</t>
+          <t>23,78; 33,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>30,68; 41,41</t>
+          <t>31,06; 41,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,04; 36,55</t>
+          <t>26,13; 36,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>26,24; 34,88</t>
+          <t>26,54; 35,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22,43; 29,14</t>
+          <t>21,94; 28,57</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26,47; 33,4</t>
+          <t>26,12; 33,53</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27,23; 34,15</t>
+          <t>27,04; 34,24</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>22,73; 28,95</t>
+          <t>22,98; 29,18</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>39,88%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,88; 30,92</t>
+          <t>21,91; 31,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>22,42; 31,97</t>
+          <t>21,99; 31,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25,75; 36,14</t>
+          <t>26,06; 36,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31,46; 45,9</t>
+          <t>30,42; 43,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>28,16; 37,85</t>
+          <t>28,45; 38,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,31; 30,25</t>
+          <t>21,92; 30,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,67; 43,36</t>
+          <t>33,06; 43,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>25,86; 52,84</t>
+          <t>38,51; 48,42</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>26,54; 33,25</t>
+          <t>26,82; 33,48</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23,45; 30,34</t>
+          <t>23,24; 29,67</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31,03; 38,06</t>
+          <t>31,16; 38,03</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30,56; 47,9</t>
+          <t>36,04; 44,2</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>14,61%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>26,99; 39,88</t>
+          <t>27,01; 40,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,51; 25,43</t>
+          <t>14,12; 25,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,82; 22,41</t>
+          <t>11,77; 22,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,26; 16,55</t>
+          <t>8,07; 15,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>22,69; 35,66</t>
+          <t>23,15; 36,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,54; 38,83</t>
+          <t>25,86; 38,65</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,31; 31,53</t>
+          <t>20,64; 31,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,63; 22,36</t>
+          <t>14,17; 21,28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>26,36; 35,6</t>
+          <t>26,92; 35,71</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21,99; 30,79</t>
+          <t>22,18; 30,8</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17,46; 25,4</t>
+          <t>17,51; 25,37</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,67; 18,22</t>
+          <t>12,17; 17,39</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>25,69%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15,6; 24,56</t>
+          <t>15,16; 24,75</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>25,08; 36,94</t>
+          <t>25,16; 37,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29,97; 41,43</t>
+          <t>29,94; 42,29</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19,23; 29,02</t>
+          <t>18,56; 28,61</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>28,25; 39,67</t>
+          <t>28,8; 40,05</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,7; 36,01</t>
+          <t>25,46; 36,3</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35,27; 48,11</t>
+          <t>35,42; 47,55</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>24,18; 33,21</t>
+          <t>23,61; 32,53</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>23,54; 31,22</t>
+          <t>23,4; 30,86</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>26,33; 34,44</t>
+          <t>26,81; 34,98</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>33,97; 42,57</t>
+          <t>34,47; 42,78</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>23,04; 29,98</t>
+          <t>22,7; 29,5</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>36,68%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>25,18; 32,61</t>
+          <t>25,54; 32,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>21,15; 28,17</t>
+          <t>21,04; 28,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24,53; 32,02</t>
+          <t>24,46; 32,1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30,45; 39,43</t>
+          <t>30,85; 39,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>34,24; 41,71</t>
+          <t>33,91; 41,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,82; 37,18</t>
+          <t>29,89; 37,97</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,73; 40,96</t>
+          <t>33,45; 40,6</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>15,68; 40,76</t>
+          <t>35,13; 41,71</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>31,05; 36,5</t>
+          <t>30,93; 36,42</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26,79; 31,8</t>
+          <t>26,68; 31,58</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30,22; 35,52</t>
+          <t>30,25; 35,56</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>18,6; 37,94</t>
+          <t>34,21; 39,62</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>21,64%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>17,76; 23,58</t>
+          <t>18,18; 24,17</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>20,49; 26,64</t>
+          <t>20,38; 26,74</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26,44; 33,27</t>
+          <t>26,5; 33,05</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,75; 20,54</t>
+          <t>16,69; 22,77</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>23,45; 30,07</t>
+          <t>23,74; 30,02</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,51; 34,15</t>
+          <t>27,87; 34,26</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,07; 36,75</t>
+          <t>30,07; 37,16</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>21,25; 26,78</t>
+          <t>20,94; 26,41</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>21,63; 26,11</t>
+          <t>21,68; 26,07</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>25,17; 29,59</t>
+          <t>24,98; 29,55</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29,66; 34,49</t>
+          <t>29,3; 34,16</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>11,7; 22,82</t>
+          <t>19,66; 23,68</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>28,8%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>23,38; 26,54</t>
+          <t>23,42; 26,53</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>23,24; 26,21</t>
+          <t>23,19; 26,29</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>27,52; 30,51</t>
+          <t>27,66; 30,61</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>19,49; 27,58</t>
+          <t>24,69; 27,92</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>29,78; 33,02</t>
+          <t>29,83; 33,03</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>28,62; 31,75</t>
+          <t>28,65; 31,85</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>32,96; 36,15</t>
+          <t>32,94; 36,2</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>24,36; 32,7</t>
+          <t>29,9; 32,58</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>26,97; 29,31</t>
+          <t>27,15; 29,25</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>26,42; 28,62</t>
+          <t>26,45; 28,67</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>30,72; 33,0</t>
+          <t>30,69; 33,0</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>23,69; 29,62</t>
+          <t>27,74; 29,88</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>116205</t>
+          <t>111142</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>114507</t>
+          <t>118810</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>230712</t>
+          <t>229952</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>42128; 68026</t>
+          <t>42193; 68118</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>60254; 91727</t>
+          <t>61921; 91935</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>73403; 107065</t>
+          <t>73748; 105844</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>93488; 137152</t>
+          <t>94601; 129694</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>46390; 74379</t>
+          <t>45188; 72480</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>61012; 94855</t>
+          <t>61349; 94111</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>83022; 115344</t>
+          <t>85395; 117566</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>100347; 129082</t>
+          <t>103458; 132657</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>96427; 133726</t>
+          <t>93653; 133083</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>131992; 177016</t>
+          <t>132364; 175865</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>166897; 214189</t>
+          <t>165669; 213132</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>206042; 256593</t>
+          <t>209460; 251739</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>126950</t>
+          <t>125554</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>138025</t>
+          <t>145638</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>264975</t>
+          <t>271191</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>122699; 164042</t>
+          <t>120006; 163310</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>106246; 145069</t>
+          <t>104322; 145313</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>121842; 163059</t>
+          <t>121035; 164796</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>104312; 154991</t>
+          <t>101485; 151651</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>155699; 196735</t>
+          <t>156023; 197561</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>114063; 152635</t>
+          <t>113430; 152927</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>144663; 188742</t>
+          <t>147591; 191025</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>121380; 157924</t>
+          <t>127106; 165218</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>289095; 347620</t>
+          <t>289044; 350868</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>229959; 286794</t>
+          <t>231414; 288885</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>280215; 342497</t>
+          <t>285086; 343031</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>234607; 297693</t>
+          <t>239659; 303945</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>64312</t>
+          <t>65149</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>106038</t>
+          <t>108425</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>170350</t>
+          <t>173573</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>57992; 87935</t>
+          <t>56969; 86792</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>59672; 91585</t>
+          <t>60149; 91788</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>79729; 111041</t>
+          <t>80076; 111467</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>51039; 78790</t>
+          <t>51431; 77931</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>80335; 113611</t>
+          <t>79755; 112291</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>104617; 141232</t>
+          <t>105918; 141394</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>87562; 122927</t>
+          <t>87892; 122346</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>91283; 121360</t>
+          <t>94234; 124315</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>146732; 190636</t>
+          <t>143558; 186938</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>175683; 221668</t>
+          <t>173340; 222561</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>178337; 223663</t>
+          <t>177070; 224251</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>150384; 191507</t>
+          <t>153692; 195121</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>120505</t>
+          <t>135071</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>194989</t>
+          <t>179968</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>315494</t>
+          <t>315039</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>78493; 110905</t>
+          <t>78574; 112081</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>83833; 119560</t>
+          <t>82231; 118138</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>95262; 133700</t>
+          <t>96429; 133933</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>98144; 143198</t>
+          <t>113337; 162563</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>104610; 140605</t>
+          <t>105663; 141188</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>82889; 117649</t>
+          <t>85252; 120152</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>126520; 167936</t>
+          <t>128028; 166975</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>121977; 249244</t>
+          <t>160766; 202109</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>193775; 242736</t>
+          <t>195804; 244475</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>178917; 231456</t>
+          <t>177320; 226378</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>235007; 288190</t>
+          <t>235937; 288009</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>239477; 375408</t>
+          <t>284712; 349134</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21966</t>
+          <t>23839</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>36998</t>
+          <t>39029</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>58965</t>
+          <t>62868</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>54863; 81074</t>
+          <t>54913; 81586</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>30848; 54078</t>
+          <t>30026; 53698</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>24964; 47328</t>
+          <t>24854; 46592</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14771; 29590</t>
+          <t>16587; 32192</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>47124; 74052</t>
+          <t>48082; 75650</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>58018; 84888</t>
+          <t>56530; 84497</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>44387; 68931</t>
+          <t>45115; 69524</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>30146; 46087</t>
+          <t>31813; 47783</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>108346; 146320</t>
+          <t>110620; 146779</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>94849; 132779</t>
+          <t>95659; 132814</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>75039; 109165</t>
+          <t>75254; 109061</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>48767; 70103</t>
+          <t>52343; 74835</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>65155</t>
+          <t>62688</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>73486</t>
+          <t>74608</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>138641</t>
+          <t>137297</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>42239; 66498</t>
+          <t>41064; 67030</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>68704; 101199</t>
+          <t>68935; 101535</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>78853; 109007</t>
+          <t>78782; 111264</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>51860; 78242</t>
+          <t>50255; 77457</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>78571; 110342</t>
+          <t>80094; 111410</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>69178; 100838</t>
+          <t>71292; 101646</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>96320; 131387</t>
+          <t>96737; 129874</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>62162; 85358</t>
+          <t>62268; 85788</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>129219; 171409</t>
+          <t>128435; 169419</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>145845; 190797</t>
+          <t>148505; 193807</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>182149; 228300</t>
+          <t>184857; 229425</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>121336; 157903</t>
+          <t>121328; 157669</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>212827</t>
+          <t>244799</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>249001</t>
+          <t>290847</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>461828</t>
+          <t>535646</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>154661; 200287</t>
+          <t>156836; 199682</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>140173; 186703</t>
+          <t>139428; 187707</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>161052; 210234</t>
+          <t>160582; 210779</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>186229; 241136</t>
+          <t>217494; 275670</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>218517; 266193</t>
+          <t>216407; 266712</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>206896; 258005</t>
+          <t>207362; 263454</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>233167; 283174</t>
+          <t>231207; 280682</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>131167; 340845</t>
+          <t>265440; 315137</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>388838; 457140</t>
+          <t>387345; 456061</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>363396; 431421</t>
+          <t>361964; 428479</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>407344; 478724</t>
+          <t>407755; 479301</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>269318; 549224</t>
+          <t>499602; 578648</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>134792</t>
+          <t>154873</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>171190</t>
+          <t>194606</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>305982</t>
+          <t>349479</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>132132; 175374</t>
+          <t>135195; 179775</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>159623; 207568</t>
+          <t>158761; 208340</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>205825; 259022</t>
+          <t>206327; 257299</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>62270; 189371</t>
+          <t>131980; 180040</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>183748; 235629</t>
+          <t>186026; 235231</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>226641; 281384</t>
+          <t>229610; 282219</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>248468; 303602</t>
+          <t>248442; 306964</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>150952; 190214</t>
+          <t>172637; 217710</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>330332; 398765</t>
+          <t>331189; 398126</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>403531; 474275</t>
+          <t>400496; 473620</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>475900; 553472</t>
+          <t>470141; 548199</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>190939; 372530</t>
+          <t>317461; 382469</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>862713</t>
+          <t>923114</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1084234</t>
+          <t>1151931</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1946946</t>
+          <t>2075045</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>765770; 869320</t>
+          <t>767116; 869016</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>795892; 897514</t>
+          <t>793953; 900175</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>934257; 1035721</t>
+          <t>939015; 1038925</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>669893; 947806</t>
+          <t>865964; 978975</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1006060; 1115428</t>
+          <t>1007614; 1115681</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1018088; 1129440</t>
+          <t>1019104; 1132904</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1168344; 1281496</t>
+          <t>1167396; 1283111</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>884215; 1187018</t>
+          <t>1105992; 1205191</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1794572; 1949930</t>
+          <t>1806499; 1946168</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1844792; 1998460</t>
+          <t>1846546; 2001610</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2131619; 2290065</t>
+          <t>2129771; 2289983</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1673995; 2093062</t>
+          <t>1999274; 2152988</t>
         </is>
       </c>
     </row>
